--- a/AAII_Financials/Quarterly/IBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IBM_QTR_FIN.xlsx
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17162000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15917000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19686000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16331000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16977000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14541000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17553000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14967000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15771000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14462000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17380000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14752000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15475000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14252000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16690000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14107000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15535000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14197000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16695000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13251000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14218000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13187000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>55179000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17560000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18123000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17571000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>21777000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18028000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>19161000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>18182000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>21761000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18756000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20003000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>19072000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>22542000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>19153000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>19289000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>18155000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>21770000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>19226000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6843000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7658000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6861000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6910000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6406000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7025000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6452000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6735000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6620000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7028000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6636000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6881000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6632000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7058000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6677000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7246000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6862000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7195000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6144000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6366000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6160000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24313000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9130000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9423000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9649000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10677000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9692000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10151000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10139000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11073000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9953000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10804000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>10825000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11492000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>10172000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>10320000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>10210000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10876000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>10213000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9907000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8950000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11928000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9361000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9977000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8031000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10440000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8420000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8949000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7743000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10267000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8022000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8501000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7510000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9632000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7430000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8289000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7335000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9500000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7107000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7852000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7027000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>30866000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8430000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8700000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>7922000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11100000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8336000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9010000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8043000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10688000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8803000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>9199000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8247000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>11050000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8981000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8969000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7945000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>10894000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>9013000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,130 +1219,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2311000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2173000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2187000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2082000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2097000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1950000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1967000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1876000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1840000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1796000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1748000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1685000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1687000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1655000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1604000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1611000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1673000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1679000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1625000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6469000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1641000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1616000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6262000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1515000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1582000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1625000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1596000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1553000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1407000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1433000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1358000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1252000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1364000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1405000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1378000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1291000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1436000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1484000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1431000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1397000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,252 +1467,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E14" s="3">
         <v>425000</v>
       </c>
-      <c r="E14" s="3">
-        <v>327000</v>
-      </c>
       <c r="F14" s="3">
+        <v>381000</v>
+      </c>
+      <c r="G14" s="3">
         <v>70000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>49000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>403000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>393000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2686000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>57000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>184000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-60000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>54000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>127000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>264000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-202000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5741000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-60000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-80000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-291000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>29000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>129000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>426000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1989000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>309000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>137000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>728000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>17000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>495000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>8000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>26000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>540000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>11000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>17000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>3000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>167000</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>997000</v>
+      </c>
+      <c r="E15" s="3">
         <v>925000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>847000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>945000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>927000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>831000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>806000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>745000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>786000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>761000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>292000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>893000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>777000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>874000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>254000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>252000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>277000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>279000</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="V15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>285000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>276000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>272000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1104000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>278000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>284000</v>
       </c>
       <c r="AB15" s="3">
         <v>284000</v>
       </c>
       <c r="AC15" s="3">
+        <v>284000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>294000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>276000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>95000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>97000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>106000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>110000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>110000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>114000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>125000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>127000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>130000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>132000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>136000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>14322000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13719000</v>
       </c>
-      <c r="E17" s="3">
-        <v>14810000</v>
-      </c>
       <c r="F17" s="3">
+        <v>14756000</v>
+      </c>
+      <c r="G17" s="3">
         <v>13527000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13867000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12742000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13712000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12852000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13417000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12984000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13349000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12612000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13190000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12807000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13377000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18608000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13813000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13574000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13827000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12438000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13306000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12944000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>52607000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15733000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16552000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>17621000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17784000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16505000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16393000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>16299000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17327000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>15760000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17227000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>17936000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>18074000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>16089000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>16846000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>16732000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>16785000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>15964000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2840000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2198000</v>
       </c>
-      <c r="E18" s="3">
-        <v>4876000</v>
-      </c>
       <c r="F18" s="3">
+        <v>4930000</v>
+      </c>
+      <c r="G18" s="3">
         <v>2804000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3110000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1799000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3841000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2115000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2354000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1478000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4031000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2140000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2285000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1445000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3313000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4501000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1722000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>623000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2868000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>813000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>912000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>243000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2572000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1827000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1571000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3993000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1523000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2768000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1883000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4434000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2996000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2776000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1136000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4468000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3064000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2443000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1423000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4985000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3262000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2024,56 +2056,57 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="E20" s="3">
         <v>64000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>59000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-38000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>126000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-132000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-28000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-133000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>70000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-43000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-64000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -2081,20 +2114,20 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -2102,17 +2135,17 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -2129,192 +2162,198 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" s="3">
         <v>1000</v>
       </c>
       <c r="AM20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>1000</v>
       </c>
-      <c r="AO20" s="3">
-        <v>0</v>
-      </c>
       <c r="AP20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3924000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3059000</v>
       </c>
-      <c r="E21" s="3">
-        <v>5664000</v>
-      </c>
       <c r="F21" s="3">
+        <v>5718000</v>
+      </c>
+      <c r="G21" s="3">
         <v>3787000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3911000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2655000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4779000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2888000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3273000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2240000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4253000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3076000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3126000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2393000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4449000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3338000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2968000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1879000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4250000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2497000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2592000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1916000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9267000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3510000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3250000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1585000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5643000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3191000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4062000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3329000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5546000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4134000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3892000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2250000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5618000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4241000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3560000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2523000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>6112000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>4390000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E22" s="3">
         <v>473000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>478000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>492000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>510000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>455000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>424000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>429000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>427000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>432000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>405000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>412000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>423000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>367000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2479000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1388000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4144000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2430000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2597000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1157000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3306000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-802000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2220000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1073000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3759000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1873000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2000000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3312000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4501000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1722000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>623000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2869000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>813000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>912000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>244000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2572000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1827000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1571000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3993000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1522000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2768000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1883000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4434000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2996000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2776000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1136000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4469000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3065000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2443000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1424000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>4985000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3263000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E24" s="3">
         <v>172000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1435000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>686000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>404000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>103000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>379000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-485000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>390000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-502000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>474000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>159000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>419000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>124000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>486000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1287000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>261000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-155000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>501000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-224000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>115000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-179000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1470000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>149000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>209000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1375000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>338000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-156000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>255000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>148000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>537000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>304000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>387000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-647000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>47000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>339000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>111000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-329000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>480000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>409000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2166000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1216000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5579000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1744000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2193000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1054000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2927000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-317000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1830000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1575000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3285000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1714000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1581000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>934000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2826000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3214000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1461000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>778000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2368000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1037000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>797000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>423000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4042000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1678000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1362000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1326000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3655000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1678000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2513000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1735000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3897000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2692000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2389000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1783000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4422000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2726000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2332000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1753000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>4505000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1216000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5600000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1744000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2194000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1055000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2914000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-330000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1834000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1605000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3288000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1704000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1583000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>927000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2827000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3214000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1461000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>778000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2367000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1038000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>796000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>422000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4042000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1678000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1362000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1325000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3655000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1678000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2513000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1734000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3897000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2692000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2389000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1782000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4424000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2726000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2332000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1753000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>4506000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2854000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3122,130 +3179,136 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>21000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>1000</v>
       </c>
       <c r="I29" s="3">
-        <v>-13000</v>
+        <v>1000</v>
       </c>
       <c r="J29" s="3">
         <v>-13000</v>
       </c>
       <c r="K29" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="L29" s="3">
         <v>4000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>30000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>3000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-10000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>2000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-117000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>18000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-69000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-45000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-35000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1252000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>529000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>532000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1548000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>20000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-150000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>15000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-1946000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>2000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-103000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-5477000</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3488,56 +3554,59 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-64000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-59000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>38000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-126000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>132000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>28000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>133000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-70000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>43000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>64000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>74000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3545,20 +3614,20 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3566,17 +3635,17 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3593,147 +3662,153 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="3">
         <v>-1000</v>
       </c>
       <c r="AM32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO32" s="3">
-        <v>0</v>
-      </c>
       <c r="AP32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1216000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5600000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1744000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2194000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1055000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2914000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-330000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1834000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1605000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3288000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1704000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1583000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>927000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2710000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3196000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1392000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>733000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2332000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2290000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1325000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>954000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5590000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1175000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3670000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1672000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2498000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1591000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1951000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2694000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2404000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1679000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1053000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2726000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2331000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1750000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>4501000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2853000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1216000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5600000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1744000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2194000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1055000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2914000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-330000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1834000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1605000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3288000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1704000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1583000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>927000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2710000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3196000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1392000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>733000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2332000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2290000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1325000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>954000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5590000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1175000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3670000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1672000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2498000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1591000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1951000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2694000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2404000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1679000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1053000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2726000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2331000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1750000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>4501000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2853000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4191,186 +4276,190 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7172000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10819000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13587000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11569000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11943000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11035000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13947000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13197000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12210000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14603000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13068000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7257000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9394000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9337000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7886000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7816000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7034000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9934000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6650000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7455000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7350000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10531000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13188000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>14393000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12041000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11218000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8172000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10087000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>45399000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>17134000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11379000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11563000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>10741000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>11949000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11972000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>10915000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>11696000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>10096000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>7826000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>9039000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>960000</v>
+      </c>
+      <c r="E42" s="3">
         <v>964000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>830000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3286000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3504000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6430000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>644000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>505000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1481000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4512000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>373000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3721000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6904000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8057000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>852000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1753000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>524000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>550000</v>
-      </c>
-      <c r="U42" s="3">
-        <v>600000</v>
       </c>
       <c r="V42" s="3">
         <v>600000</v>
@@ -4385,912 +4474,936 @@
         <v>600000</v>
       </c>
       <c r="Z42" s="3">
+        <v>600000</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1200000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2063000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>647000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>696000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>739000</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>882000</v>
       </c>
       <c r="AF42" s="3">
         <v>882000</v>
       </c>
       <c r="AG42" s="3">
+        <v>882000</v>
+      </c>
+      <c r="AH42" s="3">
         <v>620000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2944000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>967000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>895000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>620000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>623000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>601000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>605000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>712000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>931000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>7951000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8286000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9646000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7225000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7631000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7215000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8184000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6885000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7010000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7260000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8348000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6514000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6912000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6988000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14635000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13230000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13926000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14242000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15407000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15235000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16370000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16589000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>28262000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18398000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>19952000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20669000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23795000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20959000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>24738000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>27945000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>30563000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>27087000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>28340000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>29229000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>31630000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>27126000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>26958000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>25869000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>29245000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>25196000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1745000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1476000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1220000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1397000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1251000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1431000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1289000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1368000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1234000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1212000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1161000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1398000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1501000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1603000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1552000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1794000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1684000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1776000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1649000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1891000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1807000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1828000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1812000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1949000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1869000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1786000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1619000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1712000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1745000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1771000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1682000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1893000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1742000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1753000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1583000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1711000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1604000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1609000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1553000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1729000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1724000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1316000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1429000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1537000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1342000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1533000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1054000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1478000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1444000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1313000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1474000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1373000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1242000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4193000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4406000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4728000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4828000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5233000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4786000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4647000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4490000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6195000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3905000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4028000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4611000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4138000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4624000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4753000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4973000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4902000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4770000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5005000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5296000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3930000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4367000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4154000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4710000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>4552000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>4538000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>28398000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31914000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36944000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32740000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34253000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35336000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34482000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>30543000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33299000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36663000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32908000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27705000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34458000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35982000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29118000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>28999000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27896000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31330000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29539000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>29967000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>30774000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34038000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>39165000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>39845000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>39953000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>38931000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>38420000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>38121000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>77517000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>52705000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>49146000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>48257000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>46795000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>49122000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>49735000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>44742000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>45013000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>42889000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>43888000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>41433000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>1867000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1827000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1751000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1448000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1553000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1631000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1691000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1868000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1732000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1566000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1589000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1581000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1577000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1584000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7423000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6395000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7005000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6381000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7248000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7042000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7684000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8047000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9273000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8367000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9272000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9619000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10692000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9960000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10669000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10764000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>11187000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>10451000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>11301000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11798000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11576000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>13265000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>13055000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>13051000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12457000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>13043000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8804000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8999000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9028000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9074000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9257000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9065000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8929000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8969000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8730000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8798000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8721000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8481000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8096000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8133000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8212000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7890000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8123000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8667000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8917000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13391000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13810000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13935000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9771000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14673000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14483000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14497000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15006000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14964000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15200000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15309000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>10792000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10949000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11024000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>11278000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>22232000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>11057000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>10903000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>10865000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10830000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>11104000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>88554000</v>
+      </c>
+      <c r="E49" s="3">
         <v>89333000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79108000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79125000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>79759000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>78457000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71366000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72182000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>69667000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>70284000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>71214000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>70874000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>66881000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>67098000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>67133000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>65185000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>66610000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>68418000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>68154000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>74403000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>75184000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>73519000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>67504000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>72317000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>72103000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>72183000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>73457000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>73564000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>38012000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>39237000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>39352000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>39660000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>39826000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>40253000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>40530000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>40763000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>40696000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>40743000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>40887000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>41282000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>7806000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7759000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7906000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8394000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8322000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7795000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7588000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8015000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7639000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7556000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7545000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8901000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8743000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8510000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15357000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17381000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17869000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18479000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18143000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>19411000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>19362000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>19090000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>30257000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>18926000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>18389000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18173000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14611000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13011000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13254000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12911000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12905000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>12673000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12676000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12834000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>12399000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11809000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10828000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9947000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>9408000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>8744000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>152099000</v>
+      </c>
+      <c r="E54" s="3">
         <v>156229000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>151880000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>146312000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>148585000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>145667000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137175000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134339000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>133848000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>137169000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135241000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>129321000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>132213000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>133637000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>127243000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>125850000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>127503000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>133275000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>132001000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>144214000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>146814000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>148629000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>155971000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>154128000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>154200000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>153403000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>152186000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>149620000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>154652000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>130926000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>123382000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>121990000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>121622000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>125285000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>125356000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>121636000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>120495000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>117495000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>117470000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>115606000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>4395000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4039000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4756000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3867000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3974000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3585000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4032000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3274000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3631000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3588000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4132000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3342000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3732000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3728000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4051000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3806000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3707000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3453000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3955000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4248000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4214000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4140000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4033000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3985000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4719000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4172000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4896000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4042000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4724000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5711000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6558000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5384000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5518000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5736000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6451000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>5442000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>5126000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>5324000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6209000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5271000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>6545000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9453000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7224000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8749000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9765000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7711000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5857000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4389000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4364000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6255000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7246000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7221000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7627000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5756000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4760000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5937000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5982000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7690000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6787000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7575000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6442000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5198000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>14169000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10285000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9289000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11642000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8797000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8530000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14594000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10250000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10207000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>10932000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7646000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5977000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6987000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>4299000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8061000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>8340000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>7513000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>6920000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>18375000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19340000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18702000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15907000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17261000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16907000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16201000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14714000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15506000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15854000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16016000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13648000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14592000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15119000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22694000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20723000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22155000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22913000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22877000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24009000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25960000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27204000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>28720000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23723000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>24434000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>24859000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>24008000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22494000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23033000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>22910000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>21462000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>20506000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>22278000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>24020000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>23925000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>21956000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>22779000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>22817000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>22553000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>22256000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>35912000</v>
+      </c>
+      <c r="E60" s="3">
         <v>40101000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38658000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35142000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37726000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35106000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33142000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28853000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29648000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32397000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34122000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30606000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32513000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30993000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31505000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>30466000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31844000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>34056000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>33619000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>35832000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>36616000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36542000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39869000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>37993000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38442000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>40673000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>37701000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>35066000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>42351000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>38871000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>38227000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>36822000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>35442000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>35733000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>37363000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>31697000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>35966000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>36481000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>36275000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>34447000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>58727000</v>
+      </c>
+      <c r="E61" s="3">
         <v>60349000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57383000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57820000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>57954000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59124000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52539000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>55737000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>55475000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>56616000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52689000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51304000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52677000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>55920000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46189000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>44942000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>44328000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46545000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>44917000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46926000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>48735000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>51206000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>54217000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>55129000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>55449000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>52685000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>54102000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>57797000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>58445000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>39727000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35605000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35989000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37851000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>40410000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>39837000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>41327000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>37612000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>34441000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>34655000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>35563000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>10044000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9766000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9028000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11762000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11522000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11105000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10232000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11187000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10933000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10914000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10330000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12080000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12103000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12100000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27528000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30295000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>31855000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>33562000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>34469000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>39099000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>39396000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>39368000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>41158000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>39672000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>39621000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>39917000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>39398000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>38661000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>36080000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>35721000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>32621000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>29261000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>29681000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>30852000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>30431000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>28855000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>28373000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>28125000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>28148000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>28437000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>117558000</v>
+      </c>
+      <c r="E66" s="3">
         <v>123174000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119139000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>118322000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>120997000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>118715000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>109782000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>109809000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>109745000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>113836000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112628000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>106165000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109942000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>111965000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105299000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>105774000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>108094000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>114225000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>113100000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>121986000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>124872000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>127240000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>135373000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>132920000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>133649000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>133404000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>131345000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>131663000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>137007000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>114445000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>106587000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>102206000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>103102000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>107119000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>107762000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>102009000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>102076000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>99168000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>99224000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>98596000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>155937000</v>
+      </c>
+      <c r="E72" s="3">
         <v>155327000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>155648000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>151581000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>151367000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>150703000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>151163000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>149789000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>151659000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>151362000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>151276000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>149506000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>149318000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>149253000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>149825000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>148611000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>153298000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>153401000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>154209000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>161747000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>162086000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>162218000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>162717000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>162806000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>162559000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>162626000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>162954000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>160709000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>160467000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>159396000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>159206000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>158612000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>157349000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>156371000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>153126000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>155565000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>154234000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>153292000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>152759000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>149585000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>34452000</v>
+      </c>
+      <c r="E76" s="3">
         <v>32974000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32648000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27905000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27509000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26880000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27307000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24448000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24026000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23261000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22533000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23081000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22201000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21604000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21944000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20076000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19409000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19050000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18901000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22228000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21942000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21389000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20598000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21208000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20551000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19999000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20841000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17957000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17645000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16481000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>16795000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19784000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18520000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18166000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17594000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19627000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18419000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18327000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18246000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>17010000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1216000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5600000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1744000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2194000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1055000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2914000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-330000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1834000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1605000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3288000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1704000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1583000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>927000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2710000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3196000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1392000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>733000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2332000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2290000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1325000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>954000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5590000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1698000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1175000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3670000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1672000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2498000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1591000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1951000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2694000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2404000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1679000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1053000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2726000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2331000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1750000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>4501000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2853000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E83" s="3">
         <v>536000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>524000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>563000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>548000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>533000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>541000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>521000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>520000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>527000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>489000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>586000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>620000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>631000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1137000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1163000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1246000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1256000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1381000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1684000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1680000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1672000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6695000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1683000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1679000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1634000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1650000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1669000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1294000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1446000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1112000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1138000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1116000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1114000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1149000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1176000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1117000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1099000</v>
-      </c>
-      <c r="AO83" s="3">
-        <v>1127000</v>
       </c>
       <c r="AP83" s="3">
         <v>1127000</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>1127000</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2597000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5169000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4040000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3082000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1701000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4370000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4330000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2881000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2066000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4168000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4463000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3056000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2638000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3966000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1901000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1320000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3249000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2543000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2713000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2625000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4915000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18197000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4285000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3575000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4477000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3451000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3620000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2940000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4760000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4119000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4231000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4601000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5732000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3570000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3467000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3954000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3783000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>4213000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-232000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-382000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-255000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-210000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-244000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-303000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-286000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-220000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-239000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-281000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-364000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-556000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-455000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-511000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-450000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-601000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-734000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-560000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-494000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2618000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-725000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-630000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-576000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-588000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-583000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-539000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-782000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-812000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-870000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-956000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-848000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-685000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1754000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2230000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1828000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-481000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10489000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1417000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-438000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1698000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12979000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1379000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1587000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2239000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4210000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2836000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1953000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>7000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7960000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1319000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1697000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>172000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1358000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-675000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-629000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2671000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2000000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3028000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-332000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-902000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>128000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-30373000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>4162000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-853000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>455000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2969000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-635000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1764000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3810000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1705000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>350000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3687000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-951000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1590000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1576000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1574000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1569000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1563000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1549000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1546000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1543000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1536000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1522000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>1518000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1515000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1510000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1497000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1494000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1491000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1488000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1475000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1474000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1471000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1467000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1457000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5797000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1453000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1450000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1440000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1438000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1436000</v>
       </c>
       <c r="AE96" s="3">
         <v>-1436000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-1436000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1397000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1416000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1431000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1437000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1382000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1387000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1395000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1403000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1321000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1329000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1337000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-5727000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2719000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3406000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3012000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2854000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5443000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1676000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2765000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4515000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1877000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1615000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3132000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2730000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5708000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2852000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>713000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4196000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1377000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2692000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1748000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3131000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5783000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9721000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1689000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1624000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-115000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5675000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8177000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>21031000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1863000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4605000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-436000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2519000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2909000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-919000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2756000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2134000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1287000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-4182000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E101" s="3">
         <v>167000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-330000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>207000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-77000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-159000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>129000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-119000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-25000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>24000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>219000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-196000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-262000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>219000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-196000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-262000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-26000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-94000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>69000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-134000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-87000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>101000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>102000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-403000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>185000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-379000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>129000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-102000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-96000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-444000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>62000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>328000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>447000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>100000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-206000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-3645000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2778000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2040000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-426000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>865000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2999000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>945000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1264000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-287000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1676000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5813000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2148000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-110000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>721000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2966000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3263000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-850000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>242000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3108000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3002000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5361000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2365000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>817000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3057000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1911000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-35309000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28262000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5668000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>771000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1302000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>28000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1065000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-774000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1600000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2270000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1212000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-978000</v>
       </c>
     </row>
